--- a/movilizacion/entregables/Auditoria_Evaluacion_SierraCol_v5.xlsx
+++ b/movilizacion/entregables/Auditoria_Evaluacion_SierraCol_v5.xlsx
@@ -1322,25 +1322,25 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Febrero tiene 1 movilización (13-feb, INFA4562 a 12 km, 60 h) y paga el cargo fijo de 1 movilización: 133.751 (PS) y 181.054 (EC). ¿La campaña arrancó en febrero o fue un movimiento suelto?</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+          <t>Febrero tiene 1 movilización y paga el cargo fijo de 1 movilización: 133.751 (PS) y 181.054 (EC). CONFIRMADO por SierraCol: el pozo de enero tuvo problemas operativos y duró casi un mes; febrero sí fue mes de campaña. El cálculo es correcto y muestra el riesgo real: un pozo complicado deja un mes con pocas movilizaciones y el tercerizado cobra el cargo fijo igual.</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>133751</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Indeterminado</t>
+          <t>Neutro (correcto)</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>Confirmar el inicio de la campaña; si no era campaña, ese cargo no aplica.</t>
+          <t>Sin corrección. Usarlo como ejemplo del riesgo de meses con baja frecuencia.</t>
         </is>
       </c>
     </row>

--- a/movilizacion/entregables/Auditoria_Evaluacion_SierraCol_v5.xlsx
+++ b/movilizacion/entregables/Auditoria_Evaluacion_SierraCol_v5.xlsx
@@ -565,7 +565,7 @@
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>• Sesgo: de 17 hallazgos, 9 favorecen al tercerizado y solo 1 al WO (el bono del WO por mover más rápido, que no está en ningún lado); el resto son neutros o indeterminados. Es un sesgo sistemático, igual que en la evaluación previa.</t>
+          <t>• Sesgo: de 17 hallazgos, 10 favorecen al tercerizado y ninguno al WO (incluido el tope del WO: se compara contra el WO más caro posible); el resto son neutros o indeterminados. Es un sesgo sistemático, igual que en la evaluación previa.</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Bono del Work Order por mover más rápido no está considerado: las tarifas WO son los ítems 'más de X horas' (banda más lenta). Si el contratista movió más rápido, el WO real fue más caro.</t>
+          <t>CONFIRMADO por SierraCol: las tarifas WO son el tope (lo máximo, con movilización rápida); si tarda más se paga una tarifa fija menor. Ambas evaluaciones comparan contra el WO más caro posible, y el tercerizado no tiene tope. En 2025 las movilizaciones lentas habrían pagado menos en el WO.</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
@@ -1297,12 +1297,12 @@
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Favorece WO</t>
+          <t>Favorece tercerizado</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Pedir la tabla del WO por bandas de horas y aplicarla con las horas reales.</t>
+          <t>Dejar el WO en su tope como cota superior y declararlo: el ahorro calculado es el máximo posible frente al WO.</t>
         </is>
       </c>
     </row>
@@ -2035,22 +2035,22 @@
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Bono del WO por mover más rápido</t>
+          <t>Tope del WO (tarifa máxima, con piso si tarda más)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No explícito</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Parámetro (pendiente tabla)</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Favorecería al tercerizado.</t>
+          <t>El WO está acotado; el tercerizado no.</t>
         </is>
       </c>
     </row>

--- a/movilizacion/entregables/Auditoria_Evaluacion_SierraCol_v5.xlsx
+++ b/movilizacion/entregables/Auditoria_Evaluacion_SierraCol_v5.xlsx
@@ -2138,7 +2138,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>1–3 % de un pozo de 500–600 k.</t>
+          <t>0,7–3 % de un pozo de 550–650 k (campaña de 35 pozos ≈ 21 M USD).</t>
         </is>
       </c>
     </row>

--- a/movilizacion/entregables/Auditoria_Evaluacion_SierraCol_v5.xlsx
+++ b/movilizacion/entregables/Auditoria_Evaluacion_SierraCol_v5.xlsx
@@ -623,11 +623,11 @@
         <v>570244</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>524279</v>
+        <v>521576</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>5.5 usa meses fraccionarios; 6/mes en meses enteros = 5 meses de 6 + 1 de 5 (paga cargo fijo). Mi número incluye 17,3 h de bloqueo social y TM por movilización.</t>
+          <t>5.5 usa meses fraccionarios; 6/mes en meses enteros = 5 meses de 6 + 1 de 5 (paga cargo fijo). Mi número incluye además 17,3 h de bloqueo social medido; Truck Manager mensual en ambos.</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v>633169</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>587204</v>
+        <v>584501</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -665,11 +665,11 @@
         <v>180835</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>151087</v>
+        <v>132168</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>A 5/mes los meses son enteros: tu número es correcto. El mío resta el bloqueo social medido.</t>
+          <t>A 5/mes los meses son enteros: tu número es correcto. El mío resta además el bloqueo social medido (17,3 h).</t>
         </is>
       </c>
     </row>
@@ -686,11 +686,11 @@
         <v>539203</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>509454</v>
+        <v>490535</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Ídem.</t>
+          <t>Ídem (Ecotransur no tiene cargo fijo con 5).</t>
         </is>
       </c>
     </row>

--- a/movilizacion/entregables/Auditoria_Evaluacion_SierraCol_v5.xlsx
+++ b/movilizacion/entregables/Auditoria_Evaluacion_SierraCol_v5.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0;−#,##0;&quot;-&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -537,7 +537,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Se revisaron las 9 hojas (≈4.300 celdas, 2.435 fórmulas). Cada cifra se reprodujo con el motor independiente (tools/modelo.py). 'Tu número' = valor de tu archivo.</t>
+          <t>Se revisaron las 9 hojas (≈4.300 celdas, 2.435 fórmulas). Cada cifra se recalculó con un modelo de cálculo independiente.</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
     <row r="6" ht="32" customHeight="1">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>• Con esas correcciones la campaña real 2025 pasa de ahorro a pérdida para el tercerizado (Petro Star −70.830, Ecotransur −79.163) y la campaña proyectada a 6 movs/mes baja de 633 k a 570 k (Petro Star).</t>
+          <t>• Con esas correcciones la campaña real 2025 pasa de ahorro a pérdida para el tercerizado (Petro Star −70.830, Ecotransur −79.163). En la campaña proyectada a 6 movs/mes, el ahorro de Petro Star baja de 633 k a 570 k solo por usar meses enteros, y a 522 k al sumar el bloqueo social medido.</t>
         </is>
       </c>
     </row>
@@ -572,14 +572,14 @@
     <row r="8" ht="32" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>• Tu aporte que incorporé a mi simulador: los bloqueos medidos en OpenWells (22,25 h en fase de movilización en 2025 → 17,3 h por campaña de 35 pozos) y el Truck Manager mensual en la campaña real.</t>
+          <t>• Aportes de la evaluación SierraCol incorporados al Simulador: los bloqueos medidos en OpenWells (22,25 h en fase de movilización en 2025, es decir 22,25 × 35/45 = 17,3 h por campaña de 35 pozos) y el Truck Manager mensual, que pasa a ser el criterio base.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>TU NÚMERO, REPRODUCIDO Y CORREGIDO (USD, ahorro frente al WO; + = tercerizado más barato)</t>
+          <t>VALORES DE LA EVALUACIÓN, RECALCULADOS Y CORREGIDOS (USD, ahorro frente al WO; + = tercerizado más barato)</t>
         </is>
       </c>
     </row>
@@ -591,17 +591,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Tu número</t>
+          <t>Valor de la evaluación SierraCol</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Reproducido con tus premisas</t>
+          <t>Recalculado con sus mismas premisas</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Corregido / mi evaluación</t>
+          <t>Recalculado con las correcciones</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>5.5 usa meses fraccionarios; 6/mes en meses enteros = 5 meses de 6 + 1 de 5 (paga cargo fijo). Mi número incluye además 17,3 h de bloqueo social medido; Truck Manager mensual en ambos.</t>
+          <t>La sección 5.5 usa meses fraccionarios; 6/mes en meses enteros = 5 meses de 6 + 1 de 5 (paga cargo fijo). La corrección incluye además 17,3 h de bloqueo social medido; Truck Manager mensual en ambos.</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>A 5/mes los meses son enteros: tu número es correcto. El mío resta además el bloqueo social medido (17,3 h).</t>
+          <t>A 5/mes los meses son enteros: el valor de la evaluación es correcto. La corrección resta el bloqueo social medido (17,3 h).</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Simular mes a mes con conteos enteros (como hace tu propia hoja Campaña Real). Supuestos T31: 414.014 → 305.587; Resumen E25: 633.333 → 570.244.</t>
+          <t>Simular mes a mes con conteos enteros (como hace la propia hoja Campaña Real). Supuestos T31: 414.014 → 305.587; Resumen E25: 633.333 → 570.244.</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Sí: se reproduce al dólar. Orden dentro del mes, cargos fijos, descuentos y TM mensual correctos.</t>
+          <t>Sí: se reproduce al dólar. Orden dentro del mes, cargos fijos, descuentos y Truck Manager mensual correctos.</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Es la hoja más sólida. Faltan: equipos por hora excedida, Lump Sum sin descuento, bono WO y confirmar febrero.</t>
+          <t>Es la hoja más sólida. Faltan: equipos por hora excedida y Lump Sum sin descuento. Febrero confirmado como mes de campaña.</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Tu evaluación</t>
+          <t>Evaluación SierraCol (v5)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Mi evaluación</t>
+          <t>Esta revisión</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Tú: frecuencia constante con meses fraccionarios. Yo: meses enteros.</t>
+          <t>SierraCol: frecuencia constante con meses fraccionarios. Esta revisión: meses enteros.</t>
         </is>
       </c>
     </row>
@@ -1933,22 +1933,22 @@
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Truck Manager mensual en la campaña real</t>
+          <t>Truck Manager mensual</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (campaña real)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Como sensibilidad</t>
+          <t>Sí (base en todos los cálculos)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Adopto tu criterio como el más realista.</t>
+          <t>Se adopta como criterio base.</t>
         </is>
       </c>
     </row>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Ahora sí</t>
+          <t>Sí (incorporado)</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Incorporado: 17,3 h por campaña.</t>
+          <t>22,25 × 35/45 = 17,3 h por campaña.</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Tope del WO (tarifa máxima, con piso si tarda más)</t>
+          <t>Tope del WO (tarifa máxima; tarifa menor si tarda más)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>160–226 k por mes.</t>
+          <t>177 k (Petro Star) o 243 k (Ecotransur) por mes, con el Truck Manager.</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>0,7–3 % de un pozo de 550–650 k (campaña de 35 pozos ≈ 21 M USD).</t>
+          <t>0,6–2,8 % del costo de un pozo de 600 k (rango 550–650 k).</t>
         </is>
       </c>
     </row>
